--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/9.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/9.xlsx
@@ -426,13 +426,13 @@
         <v>-20.10526314043973</v>
       </c>
       <c r="E2">
-        <v>-28.50300996393618</v>
+        <v>-30.20287683761742</v>
       </c>
       <c r="F2">
-        <v>-5.321563719118257</v>
+        <v>-5.055250107936832</v>
       </c>
       <c r="G2">
-        <v>-16.75855870538292</v>
+        <v>-16.10607997450242</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-19.95266896941696</v>
       </c>
       <c r="E3">
-        <v>-26.18472109434544</v>
+        <v>-30.88491257214966</v>
       </c>
       <c r="F3">
-        <v>-5.126954768817226</v>
+        <v>-4.016084842609127</v>
       </c>
       <c r="G3">
-        <v>-16.87257554902818</v>
+        <v>-18.39478590653108</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.69788359156132</v>
       </c>
       <c r="E4">
-        <v>-26.69468613777122</v>
+        <v>-32.67939058903615</v>
       </c>
       <c r="F4">
-        <v>-4.722812023668065</v>
+        <v>-5.449304646404645</v>
       </c>
       <c r="G4">
-        <v>-15.2252994021427</v>
+        <v>-16.72709693585045</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.33391540350158</v>
       </c>
       <c r="E5">
-        <v>-27.96177127901342</v>
+        <v>-31.99611405262582</v>
       </c>
       <c r="F5">
-        <v>-5.222307326426963</v>
+        <v>-4.505780173163285</v>
       </c>
       <c r="G5">
-        <v>-16.13115073587132</v>
+        <v>-16.4076392229474</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.86225653120073</v>
       </c>
       <c r="E6">
-        <v>-29.18573629075458</v>
+        <v>-30.51727067407394</v>
       </c>
       <c r="F6">
-        <v>-4.65920564298627</v>
+        <v>-5.098637315196211</v>
       </c>
       <c r="G6">
-        <v>-16.73778503212399</v>
+        <v>-16.9748316796452</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.29648780141852</v>
       </c>
       <c r="E7">
-        <v>-30.39474828132241</v>
+        <v>-33.08482486694288</v>
       </c>
       <c r="F7">
-        <v>-4.588054487323322</v>
+        <v>-5.088655216811197</v>
       </c>
       <c r="G7">
-        <v>-16.50589621455297</v>
+        <v>-15.57754641333946</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.65074560593138</v>
       </c>
       <c r="E8">
-        <v>-31.68530223910936</v>
+        <v>-33.14615625466576</v>
       </c>
       <c r="F8">
-        <v>-4.937238677941947</v>
+        <v>-4.541162538873076</v>
       </c>
       <c r="G8">
-        <v>-16.16346497088015</v>
+        <v>-16.53859943866266</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.94592970840802</v>
       </c>
       <c r="E9">
-        <v>-33.84732252764341</v>
+        <v>-31.27649198382991</v>
       </c>
       <c r="F9">
-        <v>-4.809948314988501</v>
+        <v>-4.800344722317276</v>
       </c>
       <c r="G9">
-        <v>-14.82249705001573</v>
+        <v>-17.5700164541503</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.21398866319601</v>
       </c>
       <c r="E10">
-        <v>-32.6635364015353</v>
+        <v>-34.94465102799707</v>
       </c>
       <c r="F10">
-        <v>-4.537161305877718</v>
+        <v>-4.652687109438322</v>
       </c>
       <c r="G10">
-        <v>-14.51095650676984</v>
+        <v>-13.61662587151789</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.48618268548061</v>
       </c>
       <c r="E11">
-        <v>-33.11628191163716</v>
+        <v>-34.48021979071841</v>
       </c>
       <c r="F11">
-        <v>-4.89243009462346</v>
+        <v>-5.143501328221737</v>
       </c>
       <c r="G11">
-        <v>-14.4832224115146</v>
+        <v>-15.22947068952218</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.78524929055838</v>
       </c>
       <c r="E12">
-        <v>-35.07661076058058</v>
+        <v>-35.95866692779461</v>
       </c>
       <c r="F12">
-        <v>-4.76535669938043</v>
+        <v>-5.402392901630455</v>
       </c>
       <c r="G12">
-        <v>-13.45617697141157</v>
+        <v>-15.75578287462829</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.12124372521184</v>
       </c>
       <c r="E13">
-        <v>-34.49138700762133</v>
+        <v>-34.93038633487291</v>
       </c>
       <c r="F13">
-        <v>-4.618756210200031</v>
+        <v>-4.932961880117302</v>
       </c>
       <c r="G13">
-        <v>-13.14939202683285</v>
+        <v>-14.9724548313081</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.51465404634342</v>
       </c>
       <c r="E14">
-        <v>-35.54867700503617</v>
+        <v>-36.173794349766</v>
       </c>
       <c r="F14">
-        <v>-5.095739925223915</v>
+        <v>-5.051791294217512</v>
       </c>
       <c r="G14">
-        <v>-13.49807026993828</v>
+        <v>-14.41726972328124</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-12.97732602849431</v>
       </c>
       <c r="E15">
-        <v>-36.85688069026801</v>
+        <v>-37.46132328691582</v>
       </c>
       <c r="F15">
-        <v>-4.64456190623916</v>
+        <v>-5.070102893864781</v>
       </c>
       <c r="G15">
-        <v>-13.79324678658355</v>
+        <v>-14.02359454520604</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-12.51315186266968</v>
       </c>
       <c r="E16">
-        <v>-39.29238458107329</v>
+        <v>-38.04663308088122</v>
       </c>
       <c r="F16">
-        <v>-4.464707552099321</v>
+        <v>-4.323605689857327</v>
       </c>
       <c r="G16">
-        <v>-12.8321093423491</v>
+        <v>-12.92716172587265</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.11574394370064</v>
       </c>
       <c r="E17">
-        <v>-39.95376820989354</v>
+        <v>-39.79415761501919</v>
       </c>
       <c r="F17">
-        <v>-4.078012495020555</v>
+        <v>-3.888217218849503</v>
       </c>
       <c r="G17">
-        <v>-14.23039770395323</v>
+        <v>-13.46283778903659</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-11.78744448778868</v>
       </c>
       <c r="E18">
-        <v>-39.6276139264391</v>
+        <v>-41.3193680389356</v>
       </c>
       <c r="F18">
-        <v>-4.020302251461942</v>
+        <v>-4.391467488333908</v>
       </c>
       <c r="G18">
-        <v>-13.16441197194452</v>
+        <v>-13.15391754258503</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.52593615161474</v>
       </c>
       <c r="E19">
-        <v>-39.93713738910037</v>
+        <v>-38.2487660466876</v>
       </c>
       <c r="F19">
-        <v>-4.041239635517009</v>
+        <v>-4.35636543857115</v>
       </c>
       <c r="G19">
-        <v>-12.66688332502961</v>
+        <v>-12.26303980633054</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.32551407094403</v>
       </c>
       <c r="E20">
-        <v>-39.4490788386867</v>
+        <v>-37.92692739896246</v>
       </c>
       <c r="F20">
-        <v>-4.040754229653927</v>
+        <v>-3.944052354604237</v>
       </c>
       <c r="G20">
-        <v>-11.81100798676183</v>
+        <v>-11.9423273966681</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.17376257597597</v>
       </c>
       <c r="E21">
-        <v>-40.37046480265735</v>
+        <v>-42.20189969592044</v>
       </c>
       <c r="F21">
-        <v>-3.353977783864738</v>
+        <v>-4.037059443753207</v>
       </c>
       <c r="G21">
-        <v>-11.88453851373459</v>
+        <v>-12.13395170411774</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.06393616919968</v>
       </c>
       <c r="E22">
-        <v>-41.54582117440017</v>
+        <v>-39.08768623474157</v>
       </c>
       <c r="F22">
-        <v>-3.61023169507129</v>
+        <v>-3.355452214072012</v>
       </c>
       <c r="G22">
-        <v>-11.54226783152042</v>
+        <v>-13.67745383525646</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.98799519336759</v>
       </c>
       <c r="E23">
-        <v>-42.47454779473725</v>
+        <v>-43.15739186187986</v>
       </c>
       <c r="F23">
-        <v>-3.206746187877036</v>
+        <v>-3.133010424160091</v>
       </c>
       <c r="G23">
-        <v>-10.8990685597865</v>
+        <v>-11.47303439265764</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.9365417892388</v>
       </c>
       <c r="E24">
-        <v>-41.23979595790982</v>
+        <v>-42.77992770368151</v>
       </c>
       <c r="F24">
-        <v>-3.402329909169019</v>
+        <v>-3.378372397933209</v>
       </c>
       <c r="G24">
-        <v>-12.98229224073814</v>
+        <v>-11.74383370722448</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.8945203137578</v>
       </c>
       <c r="E25">
-        <v>-42.13608964740397</v>
+        <v>-41.30737890400029</v>
       </c>
       <c r="F25">
-        <v>-2.975185419304015</v>
+        <v>-2.931107716265504</v>
       </c>
       <c r="G25">
-        <v>-12.3210769801795</v>
+        <v>-13.44585469042012</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.84921003986578</v>
       </c>
       <c r="E26">
-        <v>-40.80900222556014</v>
+        <v>-41.74011535169927</v>
       </c>
       <c r="F26">
-        <v>-3.151140689480042</v>
+        <v>-2.871352908370059</v>
       </c>
       <c r="G26">
-        <v>-13.02520022147263</v>
+        <v>-14.50489986370575</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.79120619126231</v>
       </c>
       <c r="E27">
-        <v>-40.85406507041047</v>
+        <v>-41.66998061050547</v>
       </c>
       <c r="F27">
-        <v>-2.956454929442113</v>
+        <v>-3.081044281956776</v>
       </c>
       <c r="G27">
-        <v>-13.0220949297568</v>
+        <v>-12.49430127552187</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.71421929862844</v>
       </c>
       <c r="E28">
-        <v>-42.27988228256952</v>
+        <v>-42.97750502463617</v>
       </c>
       <c r="F28">
-        <v>-3.781853154009717</v>
+        <v>-3.292194248691614</v>
       </c>
       <c r="G28">
-        <v>-12.0604476615093</v>
+        <v>-14.73840257222716</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.61141196727427</v>
       </c>
       <c r="E29">
-        <v>-40.12256707852945</v>
+        <v>-42.39391378655667</v>
       </c>
       <c r="F29">
-        <v>-3.096330211452598</v>
+        <v>-2.960404691995218</v>
       </c>
       <c r="G29">
-        <v>-12.56592823880954</v>
+        <v>-12.9541327403811</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.47824055348578</v>
       </c>
       <c r="E30">
-        <v>-41.99793949085197</v>
+        <v>-40.97354659286584</v>
       </c>
       <c r="F30">
-        <v>-2.690302856264063</v>
+        <v>-3.660317978352978</v>
       </c>
       <c r="G30">
-        <v>-12.01803957315124</v>
+        <v>-12.69131846165497</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.31745893399728</v>
       </c>
       <c r="E31">
-        <v>-42.72322215215745</v>
+        <v>-41.39910088078865</v>
       </c>
       <c r="F31">
-        <v>-3.38532407504903</v>
+        <v>-3.312833896034578</v>
       </c>
       <c r="G31">
-        <v>-11.49773768347168</v>
+        <v>-13.76866598595446</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.13615603381941</v>
       </c>
       <c r="E32">
-        <v>-40.84694630927041</v>
+        <v>-42.09737572311239</v>
       </c>
       <c r="F32">
-        <v>-3.190726210689408</v>
+        <v>-3.270488767267558</v>
       </c>
       <c r="G32">
-        <v>-12.82227371155192</v>
+        <v>-13.8291248238654</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.939813350895465</v>
       </c>
       <c r="E33">
-        <v>-41.18206244278603</v>
+        <v>-39.63369113855739</v>
       </c>
       <c r="F33">
-        <v>-2.854237006688947</v>
+        <v>-3.5966157834633</v>
       </c>
       <c r="G33">
-        <v>-12.6231477079103</v>
+        <v>-14.51717371129259</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.730635371147985</v>
       </c>
       <c r="E34">
-        <v>-41.86597296555745</v>
+        <v>-40.75740252847974</v>
       </c>
       <c r="F34">
-        <v>-2.651068125914966</v>
+        <v>-3.224306319067429</v>
       </c>
       <c r="G34">
-        <v>-12.23303633210812</v>
+        <v>-14.36634194597786</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.518038666987952</v>
       </c>
       <c r="E35">
-        <v>-42.21904676275048</v>
+        <v>-39.28844480868661</v>
       </c>
       <c r="F35">
-        <v>-3.030779039906644</v>
+        <v>-3.225608917182877</v>
       </c>
       <c r="G35">
-        <v>-12.30663969108274</v>
+        <v>-12.99794450004781</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.311967311393946</v>
       </c>
       <c r="E36">
-        <v>-39.34093887938352</v>
+        <v>-39.63441116592461</v>
       </c>
       <c r="F36">
-        <v>-2.705856432059594</v>
+        <v>-3.683200945125163</v>
       </c>
       <c r="G36">
-        <v>-12.92982340448623</v>
+        <v>-12.71323427312495</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.119681403017328</v>
       </c>
       <c r="E37">
-        <v>-39.39957356083484</v>
+        <v>-40.27345130399102</v>
       </c>
       <c r="F37">
-        <v>-2.861002598359704</v>
+        <v>-2.537660529016263</v>
       </c>
       <c r="G37">
-        <v>-11.84298454612565</v>
+        <v>-11.98183544713377</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.943950425637125</v>
       </c>
       <c r="E38">
-        <v>-40.28171124058101</v>
+        <v>-40.27596460706528</v>
       </c>
       <c r="F38">
-        <v>-3.183308924034448</v>
+        <v>-2.653118233222503</v>
       </c>
       <c r="G38">
-        <v>-12.69608895777706</v>
+        <v>-14.4085166408754</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.791534785757678</v>
       </c>
       <c r="E39">
-        <v>-39.31366161619832</v>
+        <v>-39.77588069392423</v>
       </c>
       <c r="F39">
-        <v>-3.055795258546925</v>
+        <v>-3.438462951482728</v>
       </c>
       <c r="G39">
-        <v>-13.55752601255082</v>
+        <v>-12.91339316697482</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.66916958575605</v>
       </c>
       <c r="E40">
-        <v>-38.11340090165032</v>
+        <v>-39.74269603639603</v>
       </c>
       <c r="F40">
-        <v>-2.942678271683705</v>
+        <v>-2.89895294321138</v>
       </c>
       <c r="G40">
-        <v>-12.87920185264523</v>
+        <v>-13.38821147149033</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.582956548304898</v>
       </c>
       <c r="E41">
-        <v>-38.9884651049965</v>
+        <v>-37.15535920482458</v>
       </c>
       <c r="F41">
-        <v>-3.188061625486681</v>
+        <v>-2.757744972673052</v>
       </c>
       <c r="G41">
-        <v>-13.21097479495437</v>
+        <v>-13.4446132358429</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.535022937758288</v>
       </c>
       <c r="E42">
-        <v>-37.04330890821578</v>
+        <v>-39.05682242014229</v>
       </c>
       <c r="F42">
-        <v>-3.216752041850782</v>
+        <v>-2.890364506031951</v>
       </c>
       <c r="G42">
-        <v>-13.28282687533872</v>
+        <v>-13.1664413363601</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.529357626701104</v>
       </c>
       <c r="E43">
-        <v>-37.81918141689796</v>
+        <v>-39.00203694159749</v>
       </c>
       <c r="F43">
-        <v>-3.47714021734959</v>
+        <v>-2.987676899712044</v>
       </c>
       <c r="G43">
-        <v>-11.43817103758357</v>
+        <v>-12.71074474287942</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.569765477327925</v>
       </c>
       <c r="E44">
-        <v>-37.54894020201623</v>
+        <v>-37.99571491913898</v>
       </c>
       <c r="F44">
-        <v>-3.234489548103704</v>
+        <v>-2.533052736655292</v>
       </c>
       <c r="G44">
-        <v>-13.89566844447752</v>
+        <v>-13.34083756482336</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.661075824768206</v>
       </c>
       <c r="E45">
-        <v>-36.70901695696956</v>
+        <v>-37.3471921565005</v>
       </c>
       <c r="F45">
-        <v>-2.770023444635454</v>
+        <v>-3.067679387736383</v>
       </c>
       <c r="G45">
-        <v>-12.92606924584469</v>
+        <v>-13.33188916023071</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.802680488550676</v>
       </c>
       <c r="E46">
-        <v>-36.69785426854065</v>
+        <v>-36.16234863171161</v>
       </c>
       <c r="F46">
-        <v>-3.169256701446753</v>
+        <v>-2.720913516050635</v>
       </c>
       <c r="G46">
-        <v>-13.56388391525899</v>
+        <v>-13.45110521564541</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.991876077176576</v>
       </c>
       <c r="E47">
-        <v>-34.87974214580812</v>
+        <v>-36.5608543443866</v>
       </c>
       <c r="F47">
-        <v>-3.064465256580998</v>
+        <v>-2.687968473744705</v>
       </c>
       <c r="G47">
-        <v>-13.43155644423601</v>
+        <v>-14.89970724835538</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.223757819225012</v>
       </c>
       <c r="E48">
-        <v>-33.77286535800929</v>
+        <v>-34.76301393554941</v>
       </c>
       <c r="F48">
-        <v>-3.269521914806182</v>
+        <v>-2.875724728549629</v>
       </c>
       <c r="G48">
-        <v>-12.68985851107216</v>
+        <v>-14.553119614758</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.496812114149254</v>
       </c>
       <c r="E49">
-        <v>-34.59635477088212</v>
+        <v>-36.81801279786018</v>
       </c>
       <c r="F49">
-        <v>-2.893425809566496</v>
+        <v>-2.663906437918476</v>
       </c>
       <c r="G49">
-        <v>-13.34781288427461</v>
+        <v>-15.81164502005795</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.803515026383433</v>
       </c>
       <c r="E50">
-        <v>-34.99094788201448</v>
+        <v>-33.5910924113414</v>
       </c>
       <c r="F50">
-        <v>-3.115120882139287</v>
+        <v>-2.585999984673221</v>
       </c>
       <c r="G50">
-        <v>-15.36436217806533</v>
+        <v>-13.4523433596771</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-10.13306959879498</v>
       </c>
       <c r="E51">
-        <v>-33.10657512760172</v>
+        <v>-36.11648651119893</v>
       </c>
       <c r="F51">
-        <v>-2.996822009520749</v>
+        <v>-2.507322266647147</v>
       </c>
       <c r="G51">
-        <v>-13.89834005472771</v>
+        <v>-13.99029873344482</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-10.47354810214523</v>
       </c>
       <c r="E52">
-        <v>-34.1562097397066</v>
+        <v>-34.4075400471323</v>
       </c>
       <c r="F52">
-        <v>-3.576340388480886</v>
+        <v>-2.639557751321552</v>
       </c>
       <c r="G52">
-        <v>-15.25593684583589</v>
+        <v>-15.54450551358477</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.82188692940183</v>
       </c>
       <c r="E53">
-        <v>-32.89578824796669</v>
+        <v>-34.0213042347811</v>
       </c>
       <c r="F53">
-        <v>-3.066358577002906</v>
+        <v>-2.781510855493094</v>
       </c>
       <c r="G53">
-        <v>-14.25010869209405</v>
+        <v>-13.94824983927776</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.17072515977264</v>
       </c>
       <c r="E54">
-        <v>-30.42641363582105</v>
+        <v>-31.88957717312136</v>
       </c>
       <c r="F54">
-        <v>-2.339165164398744</v>
+        <v>-3.04518126150165</v>
       </c>
       <c r="G54">
-        <v>-14.59787487990341</v>
+        <v>-15.84372420633349</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.51014019672307</v>
       </c>
       <c r="E55">
-        <v>-31.83984547156913</v>
+        <v>-30.81643751667967</v>
       </c>
       <c r="F55">
-        <v>-3.375689600112454</v>
+        <v>-3.038671438336236</v>
       </c>
       <c r="G55">
-        <v>-14.70173000401588</v>
+        <v>-15.30078149571085</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.83128474445803</v>
       </c>
       <c r="E56">
-        <v>-32.38217099025372</v>
+        <v>-32.34813724384907</v>
       </c>
       <c r="F56">
-        <v>-3.198777771563503</v>
+        <v>-3.208236455143465</v>
       </c>
       <c r="G56">
-        <v>-15.00219842770568</v>
+        <v>-14.83653872892055</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-12.13339328640268</v>
       </c>
       <c r="E57">
-        <v>-31.52736491538084</v>
+        <v>-31.80070813495784</v>
       </c>
       <c r="F57">
-        <v>-3.077230718112398</v>
+        <v>-3.051879545671001</v>
       </c>
       <c r="G57">
-        <v>-14.42762676500085</v>
+        <v>-15.32531429342962</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-12.41506917684352</v>
       </c>
       <c r="E58">
-        <v>-33.52239772488205</v>
+        <v>-32.65652632377142</v>
       </c>
       <c r="F58">
-        <v>-3.443771533711281</v>
+        <v>-3.157382074492789</v>
       </c>
       <c r="G58">
-        <v>-14.11320935768134</v>
+        <v>-14.53727534380705</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-12.67284697244873</v>
       </c>
       <c r="E59">
-        <v>-30.31044620919562</v>
+        <v>-32.57603496252209</v>
       </c>
       <c r="F59">
-        <v>-3.081454461788875</v>
+        <v>-3.477000059376074</v>
       </c>
       <c r="G59">
-        <v>-13.83264889959195</v>
+        <v>-13.93578894586795</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-12.90596045964317</v>
       </c>
       <c r="E60">
-        <v>-31.39043518257391</v>
+        <v>-29.29738581741369</v>
       </c>
       <c r="F60">
-        <v>-3.168277971191012</v>
+        <v>-4.086585095140829</v>
       </c>
       <c r="G60">
-        <v>-15.2860114967874</v>
+        <v>-15.20359712086001</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.11869319696202</v>
       </c>
       <c r="E61">
-        <v>-29.73851126321187</v>
+        <v>-31.42512102923567</v>
       </c>
       <c r="F61">
-        <v>-2.939810180270844</v>
+        <v>-3.439161365791437</v>
       </c>
       <c r="G61">
-        <v>-13.90345815813142</v>
+        <v>-15.24352726588193</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.31814792026782</v>
       </c>
       <c r="E62">
-        <v>-29.87193595713687</v>
+        <v>-30.52736464263704</v>
       </c>
       <c r="F62">
-        <v>-3.386873731287288</v>
+        <v>-3.421658248014</v>
       </c>
       <c r="G62">
-        <v>-14.38643695740124</v>
+        <v>-13.83835462482889</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.50610252765528</v>
       </c>
       <c r="E63">
-        <v>-30.71754243706316</v>
+        <v>-32.05740241984562</v>
       </c>
       <c r="F63">
-        <v>-3.250619592852455</v>
+        <v>-3.54635291697204</v>
       </c>
       <c r="G63">
-        <v>-15.00875992896451</v>
+        <v>-15.91743184749259</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.68428951303066</v>
       </c>
       <c r="E64">
-        <v>-29.30639748068896</v>
+        <v>-30.60596989446218</v>
       </c>
       <c r="F64">
-        <v>-3.569494027808441</v>
+        <v>-2.924362712771648</v>
       </c>
       <c r="G64">
-        <v>-14.41220458860615</v>
+        <v>-15.55999390089025</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-13.85466994832361</v>
       </c>
       <c r="E65">
-        <v>-26.90170079855787</v>
+        <v>-29.99112086454474</v>
       </c>
       <c r="F65">
-        <v>-3.699015832396741</v>
+        <v>-3.257077945575617</v>
       </c>
       <c r="G65">
-        <v>-14.95862502731779</v>
+        <v>-15.26773397486508</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.02273751397987</v>
       </c>
       <c r="E66">
-        <v>-29.05589135553265</v>
+        <v>-30.17704868611467</v>
       </c>
       <c r="F66">
-        <v>-3.217094122328517</v>
+        <v>-3.091580677412195</v>
       </c>
       <c r="G66">
-        <v>-14.32518855437918</v>
+        <v>-14.63415183792274</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.18596158584019</v>
       </c>
       <c r="E67">
-        <v>-28.67746942508168</v>
+        <v>-29.5342499146219</v>
       </c>
       <c r="F67">
-        <v>-3.395940447653179</v>
+        <v>-4.007020501802109</v>
       </c>
       <c r="G67">
-        <v>-14.84714240628283</v>
+        <v>-16.36392015855579</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.33870699148831</v>
       </c>
       <c r="E68">
-        <v>-28.97487695553543</v>
+        <v>-29.31307697985027</v>
       </c>
       <c r="F68">
-        <v>-3.051919930171845</v>
+        <v>-4.183568869843468</v>
       </c>
       <c r="G68">
-        <v>-14.81465602290596</v>
+        <v>-15.38669015245494</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-14.4745610584608</v>
       </c>
       <c r="E69">
-        <v>-29.00153155354457</v>
+        <v>-26.40527589241502</v>
       </c>
       <c r="F69">
-        <v>-3.24617650590669</v>
+        <v>-4.273495650986908</v>
       </c>
       <c r="G69">
-        <v>-14.99432595041329</v>
+        <v>-15.99536540003257</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-14.59135413497478</v>
       </c>
       <c r="E70">
-        <v>-28.63839322286949</v>
+        <v>-29.45453971513888</v>
       </c>
       <c r="F70">
-        <v>-3.398376979204083</v>
+        <v>-3.470803018128959</v>
       </c>
       <c r="G70">
-        <v>-14.57455870767032</v>
+        <v>-15.53827175633432</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.68047736038442</v>
       </c>
       <c r="E71">
-        <v>-27.46675925676097</v>
+        <v>-30.20291532964648</v>
       </c>
       <c r="F71">
-        <v>-3.731345604954522</v>
+        <v>-3.809590179412723</v>
       </c>
       <c r="G71">
-        <v>-15.64039380985699</v>
+        <v>-13.88505814602415</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.72948068978618</v>
       </c>
       <c r="E72">
-        <v>-27.64659401655357</v>
+        <v>-28.8746165410056</v>
       </c>
       <c r="F72">
-        <v>-3.569767217078855</v>
+        <v>-4.196019173897695</v>
       </c>
       <c r="G72">
-        <v>-14.81219297702475</v>
+        <v>-14.534890095746</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.73112895655153</v>
       </c>
       <c r="E73">
-        <v>-28.55958871818801</v>
+        <v>-30.9953439393007</v>
       </c>
       <c r="F73">
-        <v>-3.469416483599992</v>
+        <v>-3.066414798562904</v>
       </c>
       <c r="G73">
-        <v>-13.93931964268558</v>
+        <v>-15.63856638871931</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.68512060889971</v>
       </c>
       <c r="E74">
-        <v>-27.24015894589115</v>
+        <v>-31.40196241316044</v>
       </c>
       <c r="F74">
-        <v>-3.25139244133919</v>
+        <v>-4.317518716171336</v>
       </c>
       <c r="G74">
-        <v>-13.4674162735174</v>
+        <v>-13.39419693782534</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.58775547889826</v>
       </c>
       <c r="E75">
-        <v>-27.11832940966279</v>
+        <v>-29.63554961393648</v>
       </c>
       <c r="F75">
-        <v>-3.699319903932506</v>
+        <v>-3.128529328272355</v>
       </c>
       <c r="G75">
-        <v>-15.64022497203449</v>
+        <v>-16.51301223218963</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.43220237443172</v>
       </c>
       <c r="E76">
-        <v>-28.31904070737457</v>
+        <v>-30.83800890261521</v>
       </c>
       <c r="F76">
-        <v>-3.829286729883044</v>
+        <v>-3.309501778788494</v>
       </c>
       <c r="G76">
-        <v>-14.77922987509022</v>
+        <v>-14.56628234382214</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.22160815019062</v>
       </c>
       <c r="E77">
-        <v>-30.73855002798475</v>
+        <v>-30.6113565142943</v>
       </c>
       <c r="F77">
-        <v>-3.398365101409717</v>
+        <v>-3.817790608642869</v>
       </c>
       <c r="G77">
-        <v>-15.10752674458313</v>
+        <v>-15.03362543650998</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.9620406397694</v>
       </c>
       <c r="E78">
-        <v>-28.66013442658031</v>
+        <v>-31.60396178898359</v>
       </c>
       <c r="F78">
-        <v>-3.891269812001513</v>
+        <v>-4.618178949393854</v>
       </c>
       <c r="G78">
-        <v>-14.2355505680851</v>
+        <v>-16.01557959109536</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.65886975647774</v>
       </c>
       <c r="E79">
-        <v>-28.19336196823969</v>
+        <v>-30.30536978983302</v>
       </c>
       <c r="F79">
-        <v>-4.260821252545647</v>
+        <v>-4.680782052378217</v>
       </c>
       <c r="G79">
-        <v>-14.59715318097585</v>
+        <v>-16.01404680851068</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.3132025423625</v>
       </c>
       <c r="E80">
-        <v>-29.72510698014917</v>
+        <v>-29.92578630579908</v>
       </c>
       <c r="F80">
-        <v>-4.229439327978256</v>
+        <v>-3.033577448259225</v>
       </c>
       <c r="G80">
-        <v>-15.26216067144972</v>
+        <v>-14.80364183789681</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-12.93423998671206</v>
       </c>
       <c r="E81">
-        <v>-29.81614515736237</v>
+        <v>-33.69053090783883</v>
       </c>
       <c r="F81">
-        <v>-3.913633323233433</v>
+        <v>-3.312412630261071</v>
       </c>
       <c r="G81">
-        <v>-14.86513687656154</v>
+        <v>-15.45259814832352</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-12.53244394817799</v>
       </c>
       <c r="E82">
-        <v>-29.01772084812199</v>
+        <v>-36.17412266413155</v>
       </c>
       <c r="F82">
-        <v>-4.432615335428856</v>
+        <v>-4.929110307330953</v>
       </c>
       <c r="G82">
-        <v>-14.06725236450517</v>
+        <v>-14.40885597179318</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-12.11817037377594</v>
       </c>
       <c r="E83">
-        <v>-29.91285524827018</v>
+        <v>-32.70921964732468</v>
       </c>
       <c r="F83">
-        <v>-4.303952691299682</v>
+        <v>-4.361036579168739</v>
       </c>
       <c r="G83">
-        <v>-16.12106350361316</v>
+        <v>-13.98803100975042</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-11.69727706513349</v>
       </c>
       <c r="E84">
-        <v>-30.24710191477633</v>
+        <v>-33.46584387723725</v>
       </c>
       <c r="F84">
-        <v>-3.915347684886897</v>
+        <v>-4.368984407305372</v>
       </c>
       <c r="G84">
-        <v>-12.88354197784722</v>
+        <v>-14.32277682195382</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-11.28028362051144</v>
       </c>
       <c r="E85">
-        <v>-29.47163017604383</v>
+        <v>-32.16375136767876</v>
       </c>
       <c r="F85">
-        <v>-4.610144017431871</v>
+        <v>-4.246607491954578</v>
       </c>
       <c r="G85">
-        <v>-15.31605138701074</v>
+        <v>-13.6795609974922</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.87962110640984</v>
       </c>
       <c r="E86">
-        <v>-31.41896683305924</v>
+        <v>-31.67810422967417</v>
       </c>
       <c r="F86">
-        <v>-4.68543102109299</v>
+        <v>-4.851423197354987</v>
       </c>
       <c r="G86">
-        <v>-14.27094692099099</v>
+        <v>-16.46106977267847</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.50745884428381</v>
       </c>
       <c r="E87">
-        <v>-32.87711282115906</v>
+        <v>-32.7411702956858</v>
       </c>
       <c r="F87">
-        <v>-4.285637924240582</v>
+        <v>-4.586356754581971</v>
       </c>
       <c r="G87">
-        <v>-13.64071671140717</v>
+        <v>-16.08631767290574</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-10.17073312014221</v>
       </c>
       <c r="E88">
-        <v>-33.72657076822887</v>
+        <v>-37.80646772612143</v>
       </c>
       <c r="F88">
-        <v>-4.346926551315131</v>
+        <v>-4.015391971271122</v>
       </c>
       <c r="G88">
-        <v>-13.76371175455494</v>
+        <v>-14.58649984543047</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.875465923275762</v>
       </c>
       <c r="E89">
-        <v>-34.87702958987753</v>
+        <v>-37.32461318509826</v>
       </c>
       <c r="F89">
-        <v>-4.38167385095283</v>
+        <v>-5.068497807919483</v>
       </c>
       <c r="G89">
-        <v>-13.95750446933279</v>
+        <v>-12.91228413421917</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.629796786352298</v>
       </c>
       <c r="E90">
-        <v>-34.89724243361076</v>
+        <v>-37.70363060988124</v>
       </c>
       <c r="F90">
-        <v>-4.450453407007408</v>
+        <v>-4.569508499200569</v>
       </c>
       <c r="G90">
-        <v>-15.61141494947898</v>
+        <v>-14.49169078700405</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.440166745183975</v>
       </c>
       <c r="E91">
-        <v>-36.9400574366039</v>
+        <v>-39.337085148003</v>
       </c>
       <c r="F91">
-        <v>-4.473639653462399</v>
+        <v>-5.011664937438023</v>
       </c>
       <c r="G91">
-        <v>-14.75506289265354</v>
+        <v>-14.12094279206107</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.306851458868493</v>
       </c>
       <c r="E92">
-        <v>-38.73088550344021</v>
+        <v>-40.73643342958722</v>
       </c>
       <c r="F92">
-        <v>-4.705638316721039</v>
+        <v>-4.32485840123644</v>
       </c>
       <c r="G92">
-        <v>-14.62713348137949</v>
+        <v>-14.2254219540077</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.224068125768502</v>
       </c>
       <c r="E93">
-        <v>-38.81288711077111</v>
+        <v>-42.84922241294688</v>
       </c>
       <c r="F93">
-        <v>-5.175785173307971</v>
+        <v>-5.212485182339407</v>
       </c>
       <c r="G93">
-        <v>-14.92581586575084</v>
+        <v>-14.65061518088954</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.19027303534028</v>
       </c>
       <c r="E94">
-        <v>-40.04784725740289</v>
+        <v>-41.37134133512163</v>
       </c>
       <c r="F94">
-        <v>-4.694887329114079</v>
+        <v>-4.121672891550348</v>
       </c>
       <c r="G94">
-        <v>-15.07655493579048</v>
+        <v>-14.73792916421504</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.204278226206041</v>
       </c>
       <c r="E95">
-        <v>-41.11738224853448</v>
+        <v>-45.05289560540347</v>
       </c>
       <c r="F95">
-        <v>-4.80188883558483</v>
+        <v>-5.239964855531155</v>
       </c>
       <c r="G95">
-        <v>-14.49785336752541</v>
+        <v>-15.34840865911158</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.261733807511375</v>
       </c>
       <c r="E96">
-        <v>-44.11110433755426</v>
+        <v>-44.38680462785224</v>
       </c>
       <c r="F96">
-        <v>-3.856665837749161</v>
+        <v>-4.72801212204141</v>
       </c>
       <c r="G96">
-        <v>-14.87630831248381</v>
+        <v>-16.14875290650362</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.349736673842477</v>
       </c>
       <c r="E97">
-        <v>-44.80063469656919</v>
+        <v>-45.54229911259743</v>
       </c>
       <c r="F97">
-        <v>-4.768171736645123</v>
+        <v>-4.811585075052108</v>
       </c>
       <c r="G97">
-        <v>-14.58943629932381</v>
+        <v>-13.70917713788652</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.466315527284532</v>
       </c>
       <c r="E98">
-        <v>-46.21934899724722</v>
+        <v>-47.86730823761555</v>
       </c>
       <c r="F98">
-        <v>-4.440590878419009</v>
+        <v>-4.652201703575239</v>
       </c>
       <c r="G98">
-        <v>-15.44174949059133</v>
+        <v>-15.17278918407155</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.599193842374754</v>
       </c>
       <c r="E99">
-        <v>-47.10295616680888</v>
+        <v>-50.62665689013134</v>
       </c>
       <c r="F99">
-        <v>-4.994304353192976</v>
+        <v>-4.719312033594943</v>
       </c>
       <c r="G99">
-        <v>-15.106356466735</v>
+        <v>-15.03378930851417</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.75207425301258</v>
       </c>
       <c r="E100">
-        <v>-50.72363868947961</v>
+        <v>-51.48596426816785</v>
       </c>
       <c r="F100">
-        <v>-4.651569013062021</v>
+        <v>-4.420309148612933</v>
       </c>
       <c r="G100">
-        <v>-16.05340422915431</v>
+        <v>-15.88386622626992</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.897711383209076</v>
       </c>
       <c r="E101">
-        <v>-52.92003575632438</v>
+        <v>-52.55064926363721</v>
       </c>
       <c r="F101">
-        <v>-4.284819940135258</v>
+        <v>-4.617720466531334</v>
       </c>
       <c r="G101">
-        <v>-15.43119381613936</v>
+        <v>-15.9674310167722</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.05727971613493</v>
       </c>
       <c r="E102">
-        <v>-52.45479392219836</v>
+        <v>-53.96502528621589</v>
       </c>
       <c r="F102">
-        <v>-4.108768063898389</v>
+        <v>-4.632932753702088</v>
       </c>
       <c r="G102">
-        <v>-15.21398395748947</v>
+        <v>-16.45398520522443</v>
       </c>
     </row>
   </sheetData>
